--- a/MU/2-mu末日期权开盘+-20和+-30的双买合同/data/mu_analysis.xlsx
+++ b/MU/2-mu末日期权开盘+-20和+-30的双买合同/data/mu_analysis.xlsx
@@ -456,13 +456,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>863</v>
+        <v>854.8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.911</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="3">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>872.4</v>
+        <v>855.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.916</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="4">
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>801</v>
+        <v>786.8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.841</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="5">
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>829.3</v>
+        <v>814.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.871</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="6">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>915.1</v>
+        <v>900.6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.962</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="7">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>902.5</v>
+        <v>888.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.944</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="8">
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>965.7</v>
+        <v>941.1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.009</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="9">
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>793.2</v>
+        <v>767.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.82</v>
+        <v>0.794</v>
       </c>
     </row>
   </sheetData>
@@ -645,29 +645,29 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="E2" t="n">
-        <v>-4334</v>
+        <v>-4658</v>
       </c>
       <c r="F2" t="n">
-        <v>-160.5</v>
+        <v>-166.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.5</v>
+        <v>-12.8</v>
       </c>
       <c r="H2" t="n">
         <v>8636</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0/0/27</t>
+          <t>0/0/28</t>
         </is>
       </c>
     </row>
@@ -678,29 +678,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-2694</v>
+        <v>-2870</v>
       </c>
       <c r="F3" t="n">
-        <v>-99.8</v>
+        <v>-102.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.6</v>
+        <v>-12.9</v>
       </c>
       <c r="H3" t="n">
         <v>7543</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0/0/27</t>
+          <t>0/0/28</t>
         </is>
       </c>
     </row>
@@ -711,29 +711,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="E4" t="n">
-        <v>334</v>
+        <v>224</v>
       </c>
       <c r="F4" t="n">
-        <v>12.4</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.7</v>
+        <v>-6.8</v>
       </c>
       <c r="H4" t="n">
         <v>2715</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6/21/0</t>
+          <t>6/22/0</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -866,25 +866,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>18.2</v>
+        <v>17.4</v>
       </c>
       <c r="D2" t="n">
-        <v>-1237</v>
+        <v>-1547</v>
       </c>
       <c r="E2" t="n">
-        <v>-56.2</v>
+        <v>-67.3</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>19.7</v>
       </c>
       <c r="G2" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="3">
@@ -1006,25 +1006,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-3096</v>
+        <v>-3406</v>
       </c>
       <c r="E3" t="n">
-        <v>-344</v>
+        <v>-340.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-70.59999999999999</v>
+        <v>-73.3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="4">
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="D2" t="n">
-        <v>-1959</v>
+        <v>-2206</v>
       </c>
       <c r="E2" t="n">
-        <v>-69.95999999999999</v>
+        <v>-76.06999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.13</v>
+        <v>-5.35</v>
       </c>
     </row>
     <row r="3">
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>1237</v>
+        <v>1095</v>
       </c>
       <c r="E3" t="n">
-        <v>44.18</v>
+        <v>37.76</v>
       </c>
       <c r="F3" t="n">
-        <v>5.38</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="4">
@@ -1152,19 +1152,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>39.3</v>
+        <v>37.9</v>
       </c>
       <c r="D4" t="n">
-        <v>884</v>
+        <v>736</v>
       </c>
       <c r="E4" t="n">
-        <v>31.57</v>
+        <v>25.38</v>
       </c>
       <c r="F4" t="n">
-        <v>9.970000000000001</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="5">
@@ -1174,19 +1174,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>39.3</v>
+        <v>37.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2653</v>
+        <v>2271</v>
       </c>
       <c r="E5" t="n">
-        <v>94.75</v>
+        <v>78.31</v>
       </c>
       <c r="F5" t="n">
-        <v>20.33</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="6">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="D6" t="n">
-        <v>-3230</v>
+        <v>-3791</v>
       </c>
       <c r="E6" t="n">
-        <v>-115.36</v>
+        <v>-130.72</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="7">
@@ -1218,19 +1218,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-2177</v>
+        <v>-2753</v>
       </c>
       <c r="E7" t="n">
-        <v>-77.75</v>
+        <v>-94.93000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>5.19</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="8">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="D8" t="n">
-        <v>-4226</v>
+        <v>-4825</v>
       </c>
       <c r="E8" t="n">
-        <v>-150.93</v>
+        <v>-166.38</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.62</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="9">
@@ -1262,19 +1262,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>-4683</v>
+        <v>-5292</v>
       </c>
       <c r="E9" t="n">
-        <v>-167.25</v>
+        <v>-182.48</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.19</v>
+        <v>-6.42</v>
       </c>
     </row>
     <row r="10">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4353</v>
+        <v>-4986</v>
       </c>
       <c r="E10" t="n">
-        <v>-155.46</v>
+        <v>-171.93</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.21</v>
+        <v>-3.69</v>
       </c>
     </row>
   </sheetData>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="E2" t="n">
-        <v>2330</v>
+        <v>2134</v>
       </c>
       <c r="F2" t="n">
-        <v>83.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>13.9</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="3">
@@ -1389,19 +1389,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="E3" t="n">
-        <v>940</v>
+        <v>744</v>
       </c>
       <c r="F3" t="n">
-        <v>33.6</v>
+        <v>25.7</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4">
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="E4" t="n">
-        <v>292</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>10.4</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="5">
@@ -1443,19 +1443,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="E5" t="n">
-        <v>165</v>
+        <v>-156</v>
       </c>
       <c r="F5" t="n">
-        <v>5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="6">
@@ -1470,19 +1470,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>57.1</v>
+        <v>55.2</v>
       </c>
       <c r="E6" t="n">
-        <v>152</v>
+        <v>-295</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4</v>
+        <v>-10.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="7">
@@ -1497,19 +1497,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>-44</v>
+        <v>-491</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6</v>
+        <v>-16.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="8">
@@ -1524,19 +1524,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>53.6</v>
+        <v>51.7</v>
       </c>
       <c r="E8" t="n">
-        <v>-438</v>
+        <v>-759</v>
       </c>
       <c r="F8" t="n">
-        <v>-15.6</v>
+        <v>-26.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -1551,19 +1551,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="E9" t="n">
-        <v>-767</v>
+        <v>-1214</v>
       </c>
       <c r="F9" t="n">
-        <v>-27.4</v>
+        <v>-41.9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="10">
@@ -1578,19 +1578,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="E10" t="n">
-        <v>-987</v>
+        <v>-1371</v>
       </c>
       <c r="F10" t="n">
-        <v>-35.3</v>
+        <v>-47.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -1605,52 +1605,52 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>53.6</v>
+        <v>51.7</v>
       </c>
       <c r="E11" t="n">
-        <v>-1087</v>
+        <v>-1471</v>
       </c>
       <c r="F11" t="n">
-        <v>-38.8</v>
+        <v>-50.7</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+50%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
-        <v>35.7</v>
+        <v>34.5</v>
       </c>
       <c r="E12" t="n">
-        <v>-1254</v>
+        <v>-1570</v>
       </c>
       <c r="F12" t="n">
-        <v>-44.8</v>
+        <v>-54.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>+200%</t>
+          <t>+100%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1659,73 +1659,73 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>21.4</v>
+        <v>34.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-1257</v>
+        <v>-1575</v>
       </c>
       <c r="F13" t="n">
-        <v>-44.9</v>
+        <v>-54.3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+200%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-70%</t>
+          <t>-50%</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>39.3</v>
+        <v>20.7</v>
       </c>
       <c r="E14" t="n">
-        <v>-1357</v>
+        <v>-1579</v>
       </c>
       <c r="F14" t="n">
-        <v>-48.5</v>
+        <v>-54.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+100%</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-70%</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>35.7</v>
+        <v>37.9</v>
       </c>
       <c r="E15" t="n">
-        <v>-1374</v>
+        <v>-1804</v>
       </c>
       <c r="F15" t="n">
-        <v>-49.1</v>
+        <v>-62.2</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="16">
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="E16" t="n">
-        <v>-1710</v>
+        <v>-2094</v>
       </c>
       <c r="F16" t="n">
-        <v>-61.1</v>
+        <v>-72.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="17">
@@ -1767,19 +1767,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>35.7</v>
+        <v>34.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-2353</v>
+        <v>-2737</v>
       </c>
       <c r="F17" t="n">
-        <v>-84</v>
+        <v>-94.40000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="18">
@@ -1794,19 +1794,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="E18" t="n">
-        <v>-4271</v>
+        <v>-4467</v>
       </c>
       <c r="F18" t="n">
-        <v>-152.5</v>
+        <v>-154</v>
       </c>
       <c r="G18" t="n">
-        <v>-10.3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="19">
@@ -1821,19 +1821,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="E19" t="n">
-        <v>-7383</v>
+        <v>-7829</v>
       </c>
       <c r="F19" t="n">
-        <v>-263.7</v>
+        <v>-270</v>
       </c>
       <c r="G19" t="n">
-        <v>-27.6</v>
+        <v>-29.1</v>
       </c>
     </row>
     <row r="20">
@@ -1848,19 +1848,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="E20" t="n">
-        <v>-7562</v>
+        <v>-7883</v>
       </c>
       <c r="F20" t="n">
-        <v>-270.1</v>
+        <v>-271.8</v>
       </c>
       <c r="G20" t="n">
-        <v>-22.6</v>
+        <v>-23.6</v>
       </c>
     </row>
     <row r="21">
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="E21" t="n">
-        <v>-8170</v>
+        <v>-8555</v>
       </c>
       <c r="F21" t="n">
-        <v>-291.8</v>
+        <v>-295</v>
       </c>
       <c r="G21" t="n">
-        <v>-25.3</v>
+        <v>-26.5</v>
       </c>
     </row>
   </sheetData>
@@ -1958,29 +1958,29 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-4353</v>
+        <v>-4986</v>
       </c>
       <c r="F2" t="n">
-        <v>-155.5</v>
+        <v>-171.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2</v>
+        <v>-3.7</v>
       </c>
       <c r="H2" t="n">
         <v>10225</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0/0/28</t>
+          <t>0/0/29</t>
         </is>
       </c>
     </row>
@@ -1991,29 +1991,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="E3" t="n">
-        <v>-2618</v>
+        <v>-3012</v>
       </c>
       <c r="F3" t="n">
-        <v>-93.5</v>
+        <v>-103.9</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2</v>
+        <v>-4.6</v>
       </c>
       <c r="H3" t="n">
         <v>9056</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0/0/28</t>
+          <t>0/0/29</t>
         </is>
       </c>
     </row>
@@ -2024,29 +2024,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="E4" t="n">
-        <v>158</v>
+        <v>-83</v>
       </c>
       <c r="F4" t="n">
-        <v>5.6</v>
+        <v>-2.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9</v>
+        <v>-3</v>
       </c>
       <c r="H4" t="n">
         <v>5163</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5/19/4</t>
+          <t>5/20/4</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>16.7</v>
@@ -2093,7 +2093,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
         <v>16.7</v>
@@ -2179,25 +2179,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>27.3</v>
+        <v>26.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-476</v>
+        <v>-1052</v>
       </c>
       <c r="E2" t="n">
-        <v>-21.6</v>
+        <v>-45.7</v>
       </c>
       <c r="F2" t="n">
-        <v>17.5</v>
+        <v>12.8</v>
       </c>
       <c r="G2" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="H2" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="3">
@@ -2319,25 +2319,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>-3575</v>
+        <v>-4151</v>
       </c>
       <c r="E3" t="n">
-        <v>-397.2</v>
+        <v>-415.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-49.5</v>
+        <v>-53.8</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="4">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>460.3</v>
+        <v>455.2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.484</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="3">
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>466.9</v>
+        <v>456.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.489</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="4">
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>399.6</v>
+        <v>391.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.417</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="5">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>418</v>
+        <v>409.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="6">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>500.7</v>
+        <v>490.1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.526</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="7">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>492.2</v>
+        <v>480.9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.516</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="8">
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>527</v>
+        <v>511.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.552</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="9">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>369.6</v>
+        <v>356.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.378</v>
+        <v>0.365</v>
       </c>
     </row>
   </sheetData>
@@ -2585,19 +2585,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="D2" t="n">
-        <v>-1856</v>
+        <v>-2012</v>
       </c>
       <c r="E2" t="n">
-        <v>-68.73999999999999</v>
+        <v>-71.86</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.640000000000001</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="3">
@@ -2607,19 +2607,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>875</v>
+        <v>753</v>
       </c>
       <c r="E3" t="n">
-        <v>32.41</v>
+        <v>26.89</v>
       </c>
       <c r="F3" t="n">
-        <v>4.08</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="4">
@@ -2629,19 +2629,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="D4" t="n">
-        <v>645</v>
+        <v>496</v>
       </c>
       <c r="E4" t="n">
-        <v>23.89</v>
+        <v>17.71</v>
       </c>
       <c r="F4" t="n">
-        <v>8.65</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="5">
@@ -2651,19 +2651,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1586</v>
+        <v>1343</v>
       </c>
       <c r="E5" t="n">
-        <v>58.74</v>
+        <v>47.96</v>
       </c>
       <c r="F5" t="n">
-        <v>21.55</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="6">
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="D6" t="n">
-        <v>-3076</v>
+        <v>-3375</v>
       </c>
       <c r="E6" t="n">
-        <v>-113.93</v>
+        <v>-120.54</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.54</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="7">
@@ -2695,19 +2695,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="D7" t="n">
-        <v>-2666</v>
+        <v>-2976</v>
       </c>
       <c r="E7" t="n">
-        <v>-98.73999999999999</v>
+        <v>-106.29</v>
       </c>
       <c r="F7" t="n">
-        <v>6.82</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -2717,19 +2717,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="D8" t="n">
-        <v>-3712</v>
+        <v>-4028</v>
       </c>
       <c r="E8" t="n">
-        <v>-137.48</v>
+        <v>-143.86</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.880000000000001</v>
+        <v>-13.08</v>
       </c>
     </row>
     <row r="9">
@@ -2739,19 +2739,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4998</v>
+        <v>-5319</v>
       </c>
       <c r="E9" t="n">
-        <v>-185.11</v>
+        <v>-189.96</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.79</v>
+        <v>-14.01</v>
       </c>
     </row>
     <row r="10">
@@ -2761,19 +2761,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="D10" t="n">
-        <v>-4334</v>
+        <v>-4658</v>
       </c>
       <c r="E10" t="n">
-        <v>-160.52</v>
+        <v>-166.36</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.49</v>
+        <v>-12.79</v>
       </c>
     </row>
   </sheetData>
@@ -2839,19 +2839,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E2" t="n">
-        <v>2183</v>
+        <v>2016</v>
       </c>
       <c r="F2" t="n">
-        <v>80.8</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="3">
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1408</v>
+        <v>1304</v>
       </c>
       <c r="F3" t="n">
-        <v>52.1</v>
+        <v>46.6</v>
       </c>
       <c r="G3" t="n">
-        <v>10.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2893,19 +2893,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1284</v>
+        <v>1085</v>
       </c>
       <c r="F4" t="n">
-        <v>47.6</v>
+        <v>38.8</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="5">
@@ -2920,19 +2920,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E5" t="n">
-        <v>460</v>
+        <v>293</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="G5" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="6">
@@ -2947,19 +2947,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>59.3</v>
+        <v>57.1</v>
       </c>
       <c r="E6" t="n">
-        <v>398</v>
+        <v>199</v>
       </c>
       <c r="F6" t="n">
-        <v>14.7</v>
+        <v>7.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -2974,19 +2974,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E7" t="n">
-        <v>386</v>
+        <v>155</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3</v>
+        <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="8">
@@ -3001,19 +3001,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E8" t="n">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -3028,19 +3028,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>59.3</v>
+        <v>57.1</v>
       </c>
       <c r="E9" t="n">
-        <v>-111</v>
+        <v>-342</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1</v>
+        <v>-12.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="10">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>-239</v>
+        <v>-406</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.9</v>
+        <v>-14.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="11">
@@ -3082,19 +3082,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E11" t="n">
-        <v>-438</v>
+        <v>-637</v>
       </c>
       <c r="F11" t="n">
-        <v>-16.2</v>
+        <v>-22.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="12">
@@ -3109,19 +3109,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="E12" t="n">
-        <v>-594</v>
+        <v>-698</v>
       </c>
       <c r="F12" t="n">
-        <v>-22</v>
+        <v>-24.9</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="13">
@@ -3136,19 +3136,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="E13" t="n">
-        <v>-888</v>
+        <v>-1054</v>
       </c>
       <c r="F13" t="n">
-        <v>-32.9</v>
+        <v>-37.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-2</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="14">
@@ -3163,19 +3163,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E14" t="n">
-        <v>-1147</v>
+        <v>-1250</v>
       </c>
       <c r="F14" t="n">
-        <v>-42.5</v>
+        <v>-44.7</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -3190,19 +3190,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E15" t="n">
-        <v>-1337</v>
+        <v>-1567</v>
       </c>
       <c r="F15" t="n">
-        <v>-49.5</v>
+        <v>-56</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.8</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -3217,19 +3217,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="E16" t="n">
-        <v>-1761</v>
+        <v>-1960</v>
       </c>
       <c r="F16" t="n">
-        <v>-65.2</v>
+        <v>-70</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.699999999999999</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="17">
@@ -3244,19 +3244,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="E17" t="n">
-        <v>-2037</v>
+        <v>-2140</v>
       </c>
       <c r="F17" t="n">
-        <v>-75.40000000000001</v>
+        <v>-76.40000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.6</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="18">
@@ -3271,19 +3271,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="E18" t="n">
-        <v>-2634</v>
+        <v>-2865</v>
       </c>
       <c r="F18" t="n">
-        <v>-97.59999999999999</v>
+        <v>-102.3</v>
       </c>
       <c r="G18" t="n">
-        <v>-15.4</v>
+        <v>-17.4</v>
       </c>
     </row>
     <row r="19">
@@ -3298,19 +3298,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="E19" t="n">
-        <v>-3245</v>
+        <v>-3412</v>
       </c>
       <c r="F19" t="n">
-        <v>-120.2</v>
+        <v>-121.9</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.1</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="20">
@@ -3325,19 +3325,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="E20" t="n">
-        <v>-4397</v>
+        <v>-4596</v>
       </c>
       <c r="F20" t="n">
-        <v>-162.8</v>
+        <v>-164.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-22</v>
+        <v>-23.5</v>
       </c>
     </row>
     <row r="21">
@@ -3352,19 +3352,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="E21" t="n">
-        <v>-5549</v>
+        <v>-5779</v>
       </c>
       <c r="F21" t="n">
-        <v>-205.5</v>
+        <v>-206.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-30.9</v>
+        <v>-32.4</v>
       </c>
     </row>
   </sheetData>
